--- a/plantillas/37.xlsx
+++ b/plantillas/37.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$2</definedName>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/37.xlsx
+++ b/plantillas/37.xlsx
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/37.xlsx
+++ b/plantillas/37.xlsx
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
